--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487414_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487414_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5594</v>
+        <v>5.6747</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8751</v>
+        <v>3.2844</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6844</v>
+        <v>2.3903</v>
       </c>
       <c r="G2" t="n">
         <v>4.8901</v>
@@ -610,13 +610,13 @@
         <v>2.3502</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4574</v>
+        <v>0.5727</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2088</v>
+        <v>0.2005</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6662</v>
+        <v>0.3721</v>
       </c>
       <c r="V2" t="n">
         <v>-1.159</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ FERNANDEZ</t>
+          <t>D. CUETOS FERNANDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2167</v>
+        <v>5.2254</v>
       </c>
       <c r="E3" t="n">
-        <v>2.549</v>
+        <v>3.3658</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6677</v>
+        <v>1.8595</v>
       </c>
       <c r="G3" t="n">
-        <v>0.443</v>
+        <v>3.7641</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0044</v>
+        <v>0.3181</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4386</v>
+        <v>3.446</v>
       </c>
       <c r="J3" t="n">
-        <v>1.044</v>
+        <v>3.9475</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6158</v>
+        <v>1.1993</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4283</v>
+        <v>2.7482</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.601</v>
+        <v>-0.1834</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.8812</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0104</v>
+        <v>0.6978</v>
       </c>
       <c r="P3" t="n">
-        <v>2.7419</v>
+        <v>1.5668</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7419</v>
+        <v>2.546</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9155</v>
+        <v>-0.1056</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8379</v>
+        <v>0.3976</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0776</v>
+        <v>-0.5031</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.8837</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3329</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9025</v>
+        <v>3.9422</v>
       </c>
       <c r="E4" t="n">
-        <v>1.789</v>
+        <v>2.096</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1136</v>
+        <v>1.8463</v>
       </c>
       <c r="G4" t="n">
         <v>2.026</v>
@@ -766,13 +766,13 @@
         <v>1.5668</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0723</v>
+        <v>0.112</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.31</v>
+        <v>-0.0029</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3823</v>
+        <v>0.115</v>
       </c>
       <c r="V4" t="n">
         <v>1.2166</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. CUETOS FERNANDEZ</t>
+          <t>R. FERNANDEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4138</v>
+        <v>3.4782</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0355</v>
+        <v>1.7303</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3784</v>
+        <v>1.7479</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7641</v>
+        <v>0.443</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3181</v>
+        <v>0.0044</v>
       </c>
       <c r="I5" t="n">
-        <v>3.446</v>
+        <v>0.4386</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9475</v>
+        <v>1.044</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1993</v>
+        <v>0.6158</v>
       </c>
       <c r="L5" t="n">
-        <v>2.7482</v>
+        <v>0.4283</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1834</v>
+        <v>-0.601</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8812</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6978</v>
+        <v>0.0104</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5668</v>
+        <v>2.7419</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.546</v>
+        <v>2.7419</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.9171</v>
+        <v>1.177</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9328</v>
+        <v>1.0192</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9843</v>
+        <v>0.1578</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.8837</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.3329</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7354</v>
+        <v>2.8737</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4198</v>
+        <v>0.3175</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3156</v>
+        <v>2.5562</v>
       </c>
       <c r="G6" t="n">
         <v>1.067</v>
@@ -922,13 +922,13 @@
         <v>1.5668</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2313</v>
+        <v>-0.0931</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0129</v>
+        <v>-0.1153</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2184</v>
+        <v>0.0222</v>
       </c>
       <c r="V6" t="n">
         <v>0.3329</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5547</v>
+        <v>2.8617</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.576</v>
+        <v>-0.269</v>
       </c>
       <c r="F7" t="n">
         <v>3.1307</v>
@@ -1000,10 +1000,10 @@
         <v>2.7419</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5393</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2952</v>
+        <v>0.6022</v>
       </c>
       <c r="U7" t="n">
         <v>0.2441</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4529</v>
+        <v>1.9504</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0465</v>
+        <v>0.3302</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4064</v>
+        <v>1.6202</v>
       </c>
       <c r="G8" t="n">
         <v>1.0872</v>
@@ -1078,13 +1078,13 @@
         <v>1.5668</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5776</v>
+        <v>1.0751</v>
       </c>
       <c r="T8" t="n">
-        <v>1.2745</v>
+        <v>0.5581</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3031</v>
+        <v>0.517</v>
       </c>
       <c r="V8" t="n">
         <v>1.159</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. DIARRA</t>
+          <t>A. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.025</v>
+        <v>-0.0851</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1242</v>
+        <v>-0.4716</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1493</v>
+        <v>0.3866</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6359</v>
+        <v>-1.0444</v>
       </c>
       <c r="H9" t="n">
-        <v>1.459</v>
+        <v>-2.6002</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8231000000000001</v>
+        <v>1.5558</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2172</v>
+        <v>0.0253</v>
       </c>
       <c r="K9" t="n">
-        <v>2.3392</v>
+        <v>-1.242</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.122</v>
+        <v>1.2673</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5813</v>
+        <v>-1.0698</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8801</v>
+        <v>-1.3582</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2988</v>
+        <v>0.2885</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.3294</v>
+        <v>0.3917</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.8962</v>
+        <v>-0.9792</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5668</v>
+        <v>1.3709</v>
       </c>
       <c r="S9" t="n">
-        <v>4.3269</v>
+        <v>0.5101</v>
       </c>
       <c r="T9" t="n">
-        <v>3.2794</v>
+        <v>0.4823</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0474</v>
+        <v>0.0278</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6083</v>
+        <v>0.0576</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8837</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. MIRANDA GARCIA</t>
+          <t>D. DIARRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9931</v>
+        <v>-2.0504</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0856</v>
+        <v>-2.4779</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0925</v>
+        <v>0.4275</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0444</v>
+        <v>0.6359</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.6002</v>
+        <v>1.459</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5558</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0253</v>
+        <v>1.2172</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.242</v>
+        <v>2.3392</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2673</v>
+        <v>-1.122</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0698</v>
+        <v>-0.5813</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3582</v>
+        <v>-0.8801</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2885</v>
+        <v>0.2988</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3917</v>
+        <v>-3.3294</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9792</v>
+        <v>-4.8962</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3709</v>
+        <v>1.5668</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.398</v>
+        <v>1.2514</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1317</v>
+        <v>0.9257</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2662</v>
+        <v>0.3257</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0576</v>
+        <v>-0.6083</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0576</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4886</v>
+        <v>-3.0479</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3497</v>
+        <v>-3.0427</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1389</v>
+        <v>-0.0053</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1089</v>
@@ -1312,13 +1312,13 @@
         <v>0.7834</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.163</v>
+        <v>-0.7224</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.297</v>
+        <v>0.01</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.866</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0865</v>
+        <v>-4.5305</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5802</v>
+        <v>-3.8638</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5063</v>
+        <v>-0.6667</v>
       </c>
       <c r="G12" t="n">
         <v>-4.0336</v>
@@ -1390,13 +1390,13 @@
         <v>2.7419</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1069</v>
+        <v>0.449</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5652</v>
+        <v>0.1511</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4583</v>
+        <v>0.2979</v>
       </c>
       <c r="V12" t="n">
         <v>-2.7086</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>16.2922</v>
+        <v>16.2924</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9992000000000001</v>
+        <v>0.9991999999999996</v>
       </c>
       <c r="F13" t="n">
-        <v>15.2934</v>
+        <v>15.2932</v>
       </c>
       <c r="G13" t="n">
-        <v>5.979200000000001</v>
+        <v>5.979199999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6770000000000009</v>
+        <v>0.677</v>
       </c>
       <c r="I13" t="n">
         <v>5.302099999999999</v>
@@ -1444,10 +1444,10 @@
         <v>8.161799999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>7.108899999999998</v>
+        <v>7.108899999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>1.053100000000001</v>
+        <v>1.0531</v>
       </c>
       <c r="M13" t="n">
         <v>-2.1826</v>
@@ -1459,7 +1459,7 @@
         <v>4.2491</v>
       </c>
       <c r="P13" t="n">
-        <v>7.8339</v>
+        <v>7.833899999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-13.7091</v>
@@ -1468,13 +1468,13 @@
         <v>21.5434</v>
       </c>
       <c r="S13" t="n">
-        <v>5.072700000000001</v>
+        <v>5.0725</v>
       </c>
       <c r="T13" t="n">
-        <v>4.2286</v>
+        <v>4.2285</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8441000000000003</v>
+        <v>0.8440999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-2.5935</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9852</v>
+        <v>2.7492</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6324</v>
+        <v>1.5301</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3528</v>
+        <v>1.2191</v>
       </c>
       <c r="G14" t="n">
         <v>2.5156</v>
@@ -1546,13 +1546,13 @@
         <v>0.7834</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3138</v>
+        <v>-0.5498</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3611</v>
+        <v>0.2588</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.8085</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1446</v>
+        <v>0.5521</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2097</v>
+        <v>0.302</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3542</v>
+        <v>0.2501</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5821</v>
@@ -1624,13 +1624,13 @@
         <v>1.9585</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.528</v>
+        <v>-0.1204</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-0.137</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1208</v>
+        <v>0.0166</v>
       </c>
       <c r="V15" t="n">
         <v>0.2754</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1266</v>
+        <v>0.1515</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3404</v>
+        <v>0.4427</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2138</v>
+        <v>-0.2912</v>
       </c>
       <c r="G16" t="n">
         <v>1.0046</v>
@@ -1702,13 +1702,13 @@
         <v>1.3709</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5278</v>
+        <v>-0.5029</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3935</v>
+        <v>-0.2911</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1343</v>
+        <v>-0.2117</v>
       </c>
       <c r="V16" t="n">
         <v>1.2166</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0282</v>
+        <v>-0.6825</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2502</v>
+        <v>0.3526</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2784</v>
+        <v>-1.035</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6419</v>
@@ -1780,13 +1780,13 @@
         <v>0.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1904</v>
+        <v>0.1553</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1494</v>
+        <v>-0.0471</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.041</v>
+        <v>0.2023</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MONTEAGUDO FERNANDEZ</t>
+          <t>P. FERNÁNDEZ CARBALLO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5127</v>
+        <v>-1.3283</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.6497</v>
+        <v>-2.7137</v>
       </c>
       <c r="F18" t="n">
-        <v>1.137</v>
+        <v>1.3854</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9942</v>
+        <v>-1.6942</v>
       </c>
       <c r="H18" t="n">
-        <v>0.16</v>
+        <v>2.9806</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8343</v>
+        <v>-4.6748</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4287</v>
+        <v>-0.5848</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4287</v>
+        <v>4.4045</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-4.9892</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5655</v>
+        <v>-1.1094</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2687</v>
+        <v>-1.4239</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8343</v>
+        <v>0.3144</v>
       </c>
       <c r="P18" t="n">
-        <v>-4.1128</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.8962</v>
+        <v>-3.917</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7834</v>
+        <v>2.546</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1139</v>
+        <v>-0.3058</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3258</v>
+        <v>-0.2547</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2119</v>
+        <v>-0.0512</v>
       </c>
       <c r="V18" t="n">
-        <v>1.492</v>
+        <v>2.0427</v>
       </c>
       <c r="W18" t="n">
-        <v>1.492</v>
+        <v>2.0427</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.651</v>
+        <v>-1.5441</v>
       </c>
       <c r="E19" t="n">
         <v>-1.239</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.412</v>
+        <v>-0.3051</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0537</v>
@@ -1936,13 +1936,13 @@
         <v>0.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2851</v>
+        <v>-0.1782</v>
       </c>
       <c r="T19" t="n">
         <v>-0.22</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.0418</v>
       </c>
       <c r="V19" t="n">
         <v>0.2754</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7961</v>
+        <v>-1.6625</v>
       </c>
       <c r="E20" t="n">
         <v>-1.5978</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1983</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6476</v>
@@ -2014,13 +2014,13 @@
         <v>0.5875</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7361</v>
+        <v>-0.6024</v>
       </c>
       <c r="T20" t="n">
         <v>-0.4158</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3202</v>
+        <v>-0.1866</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. FERNÁNDEZ CARBALLO</t>
+          <t>A. MONTEAGUDO FERNANDEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8649</v>
+        <v>-2.0114</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.3278</v>
+        <v>-2.8544</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4628</v>
+        <v>0.843</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6942</v>
+        <v>0.9942</v>
       </c>
       <c r="H21" t="n">
-        <v>2.9806</v>
+        <v>0.16</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.6748</v>
+        <v>0.8343</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5848</v>
+        <v>0.4287</v>
       </c>
       <c r="K21" t="n">
-        <v>4.4045</v>
+        <v>0.4287</v>
       </c>
       <c r="L21" t="n">
-        <v>-4.9892</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1094</v>
+        <v>0.5655</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4239</v>
+        <v>-0.2687</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3144</v>
+        <v>0.8343</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3709</v>
+        <v>-4.1128</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.917</v>
+        <v>-4.8962</v>
       </c>
       <c r="R21" t="n">
-        <v>2.546</v>
+        <v>0.7834</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8424</v>
+        <v>-0.3848</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8687</v>
+        <v>0.1212</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0262</v>
+        <v>-0.5059</v>
       </c>
       <c r="V21" t="n">
-        <v>2.0427</v>
+        <v>1.492</v>
       </c>
       <c r="W21" t="n">
-        <v>2.0427</v>
+        <v>1.492</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.27</v>
+        <v>-2.2073</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8704</v>
+        <v>0.6657</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.1403</v>
+        <v>-2.873</v>
       </c>
       <c r="G22" t="n">
         <v>-1.4209</v>
@@ -2170,13 +2170,13 @@
         <v>0.5875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.22</v>
+        <v>-0.1573</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1476</v>
+        <v>-0.0571</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3676</v>
+        <v>-0.1003</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2166</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4034</v>
+        <v>-2.8616</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5156</v>
+        <v>-4.0273</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1122</v>
+        <v>1.1656</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8571</v>
@@ -2248,13 +2248,13 @@
         <v>0.9792</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1368</v>
+        <v>-0.3214</v>
       </c>
       <c r="T23" t="n">
-        <v>1.1204</v>
+        <v>0.6087</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9836</v>
+        <v>-0.9301</v>
       </c>
       <c r="V23" t="n">
         <v>0.2754</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1953</v>
+        <v>-3.0128</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7336</v>
+        <v>-2.6312</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4617</v>
+        <v>-0.3815</v>
       </c>
       <c r="G24" t="n">
         <v>-0.9997</v>
@@ -2326,13 +2326,13 @@
         <v>1.1751</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4122</v>
+        <v>-1.2296</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8316</v>
+        <v>-0.7292999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5805</v>
+        <v>-0.5004</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8272</v>
+        <v>-3.7526</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.1136</v>
+        <v>-3.5229</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7136</v>
+        <v>-0.2296</v>
       </c>
       <c r="G25" t="n">
         <v>-1.5964</v>
@@ -2404,13 +2404,13 @@
         <v>1.7626</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2677</v>
+        <v>-0.1931</v>
       </c>
       <c r="T25" t="n">
-        <v>0.7287</v>
+        <v>0.3194</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9964</v>
+        <v>-0.5124</v>
       </c>
       <c r="V25" t="n">
         <v>-1.7673</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-16.2924</v>
+        <v>-15.6103</v>
       </c>
       <c r="E26" t="n">
-        <v>-15.2934</v>
+        <v>-15.2932</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.9990999999999994</v>
+        <v>-0.3169000000000004</v>
       </c>
       <c r="G26" t="n">
         <v>-5.979200000000001</v>
@@ -2482,13 +2482,13 @@
         <v>13.7092</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.0728</v>
+        <v>-4.390400000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.8441000000000004</v>
+        <v>-0.8439999999999998</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.2286</v>
+        <v>-3.5464</v>
       </c>
       <c r="V26" t="n">
         <v>2.5936</v>
